--- a/02_HRvLR_groups/Figures/F3_People/c_data/f3_people.xlsx
+++ b/02_HRvLR_groups/Figures/F3_People/c_data/f3_people.xlsx
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>98d1cf042cfd5f72a407fcaa4643e157</t>
+    <t>75ce427b8318639baadc2acbeb3fc530</t>
   </si>
   <si>
     <t>02_HRvLR_groups/06_Classification/02_Sets/c_data/set_classification.xlsx</t>
   </si>
   <si>
-    <t>60c9ad5acada160169dea6ef773fab92</t>
+    <t>0e611e56311bca684897631c4abdc653</t>
   </si>
   <si>
     <t>02_HRvLR_groups/06_Classification/03_Modules/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>2ee0ce9d570cc74e8db89350d722354c</t>
+    <t>c0c45bca5563693d6d46b51dac0566c0</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>565567433febae9b6a932909646fd1fd</t>
+    <t>1a529f40380df0880e975dbf8028b316</t>
   </si>
   <si>
     <t>continuous</t>
@@ -11913,7 +11913,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>6981dbb51aef4b50cb02881f1fa1e4bd</t>
+    <t>40ba0b9472959680583a47b54709babd</t>
   </si>
   <si>
     <t>corrected</t>

--- a/02_HRvLR_groups/Figures/F3_People/c_data/f3_people.xlsx
+++ b/02_HRvLR_groups/Figures/F3_People/c_data/f3_people.xlsx
@@ -258,7 +258,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>input</t>
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>75ce427b8318639baadc2acbeb3fc530</t>
+    <t>2e8d3535382cbd1929ec7721ef50ba71</t>
   </si>
   <si>
     <t>02_HRvLR_groups/06_Classification/02_Sets/c_data/set_classification.xlsx</t>
   </si>
   <si>
-    <t>0e611e56311bca684897631c4abdc653</t>
+    <t>92d69975d0bc710233195c12f095bcc2</t>
   </si>
   <si>
     <t>02_HRvLR_groups/06_Classification/03_Modules/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>c0c45bca5563693d6d46b51dac0566c0</t>
+    <t>ed50542f58eee425336318a695460d35</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>1a529f40380df0880e975dbf8028b316</t>
+    <t>e96955e87c5712155dfca5fa1b35eb08</t>
   </si>
   <si>
     <t>continuous</t>
@@ -11913,13 +11913,13 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>40ba0b9472959680583a47b54709babd</t>
+    <t>53a8d72f35199120ea36dfc0a0edd388</t>
   </si>
   <si>
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Trunk/03_Quantification/c_data/DAList_corrected.rds</t>
+    <t>01_Processing/03_Quantification/c_data/DAList_corrected.rds</t>
   </si>
   <si>
     <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>

--- a/02_HRvLR_groups/Figures/F3_People/c_data/f3_people.xlsx
+++ b/02_HRvLR_groups/Figures/F3_People/c_data/f3_people.xlsx
@@ -11886,25 +11886,25 @@
     <t>LR_S30</t>
   </si>
   <si>
-    <t>2e8d3535382cbd1929ec7721ef50ba71</t>
+    <t>b01ac1f6d6d70cf871c6751d533234fd</t>
   </si>
   <si>
     <t>02_HRvLR_groups/06_Classification/02_Sets/c_data/set_classification.xlsx</t>
   </si>
   <si>
-    <t>92d69975d0bc710233195c12f095bcc2</t>
+    <t>2d5c57240ac4c245f6b3ae6409d38693</t>
   </si>
   <si>
     <t>02_HRvLR_groups/06_Classification/03_Modules/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>ed50542f58eee425336318a695460d35</t>
+    <t>3160dbe9810c780b4924a19c1e8f2f4f</t>
   </si>
   <si>
     <t>associate</t>
   </si>
   <si>
-    <t>e96955e87c5712155dfca5fa1b35eb08</t>
+    <t>9ac893e6ae1926d745c3c47a1bb5b588</t>
   </si>
   <si>
     <t>continuous</t>
@@ -11913,7 +11913,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>53a8d72f35199120ea36dfc0a0edd388</t>
+    <t>400e71a7f9b28b71965d7d0a160d06c9</t>
   </si>
   <si>
     <t>corrected</t>
